--- a/05_Professional_Speaking/professional training log_langgeng pambudi.xlsx
+++ b/05_Professional_Speaking/professional training log_langgeng pambudi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/32ee07e9fbf80e50/Documents/A-Langgeng/01_project git_portfolio/05_Professional_Speaking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="8_{6803125A-1F25-49FF-8079-9A2BF79D737C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{432D7CBF-27DA-4EF8-85A6-E5CECC8E878E}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{6803125A-1F25-49FF-8079-9A2BF79D737C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51012342-59D8-4BA8-956E-C410A5FAD5A4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A595F7D5-28CC-4199-858D-34D4E053B8BB}"/>
   </bookViews>
@@ -69,9 +69,6 @@
     <t>Gizi Nusantara</t>
   </si>
   <si>
-    <t>CT Arsya &amp; MI Al-Amanah Ciparahu Bogor</t>
-  </si>
-  <si>
     <t>GMP focusing in school catering</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
   </si>
   <si>
     <t>Bogor - Offline</t>
+  </si>
+  <si>
+    <t>CT Arsa &amp; MI Al-Amanah Ciparahu Bogor</t>
   </si>
 </sst>
 </file>
@@ -536,7 +536,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>5</v>
@@ -562,10 +562,10 @@
         <v>50</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -582,16 +582,16 @@
         <v>9</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="5">
         <v>100</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -608,16 +608,16 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F6" s="5">
         <v>8</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -634,16 +634,16 @@
         <v>9</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F7" s="5">
         <v>100</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -666,7 +666,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>11</v>
@@ -692,10 +692,10 @@
         <v>140</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -718,10 +718,10 @@
         <v>200</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
